--- a/data/trans_camb/IP13-Dificultad-trans_camb.xlsx
+++ b/data/trans_camb/IP13-Dificultad-trans_camb.xlsx
@@ -40,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -66,13 +66,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -513,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -524,9 +517,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -542,68 +532,50 @@
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Niña</t>
         </is>
       </c>
-      <c r="G1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012/2007</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
     </row>
@@ -616,9 +588,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -631,15 +600,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr"/>
-      <c r="K4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="n">
+        <v>-3.568851656428067</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-0.8996809826707669</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-0.5732004708785404</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-1.380237656506629</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>-2.124343475145144</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>-1.090886349860881</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
@@ -648,15 +626,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr"/>
-      <c r="D5" s="5" t="inlineStr"/>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="5" t="inlineStr"/>
-      <c r="G5" s="5" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr"/>
-      <c r="J5" s="5" t="inlineStr"/>
-      <c r="K5" s="5" t="inlineStr"/>
+      <c r="C5" s="5" t="n">
+        <v>-7.381691028914647</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-5.894575714337019</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-4.625912744322331</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-5.52385179475106</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>-4.780274825030939</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>-4.400448893311825</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
@@ -665,15 +652,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="n">
+        <v>0.02315082987677886</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>5.225362370819491</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>3.008471377417028</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>4.731166013601541</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>0.3863762503749096</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>2.968323534172099</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
@@ -682,15 +678,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="6" t="inlineStr"/>
-      <c r="I7" s="6" t="inlineStr"/>
-      <c r="J7" s="6" t="inlineStr"/>
-      <c r="K7" s="6" t="inlineStr"/>
+      <c r="C7" s="6" t="n">
+        <v>-0.406928595649922</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>-0.1025836751022538</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>-0.07991992070453245</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>-0.192443114871051</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.2658555718083728</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.1365213383397889</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
@@ -699,15 +704,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr"/>
-      <c r="D8" s="6" t="inlineStr"/>
-      <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="6" t="inlineStr"/>
-      <c r="G8" s="6" t="inlineStr"/>
-      <c r="H8" s="6" t="inlineStr"/>
-      <c r="I8" s="6" t="inlineStr"/>
-      <c r="J8" s="6" t="inlineStr"/>
-      <c r="K8" s="6" t="inlineStr"/>
+      <c r="C8" s="6" t="n">
+        <v>-0.6781386794371064</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>-0.5659175936449024</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>-0.5001465817236079</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>-0.6647274200685707</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.5026283405358581</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.4833326560134165</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
@@ -716,15 +730,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr"/>
-      <c r="D9" s="6" t="inlineStr"/>
-      <c r="E9" s="6" t="inlineStr"/>
-      <c r="F9" s="6" t="inlineStr"/>
-      <c r="G9" s="6" t="inlineStr"/>
-      <c r="H9" s="6" t="inlineStr"/>
-      <c r="I9" s="6" t="inlineStr"/>
-      <c r="J9" s="6" t="inlineStr"/>
-      <c r="K9" s="6" t="inlineStr"/>
+      <c r="C9" s="6" t="n">
+        <v>0.02788599725137047</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>0.7467081111541191</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>0.623930314973773</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>0.9017974664656999</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.06911964934654929</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.4763956031795497</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -737,15 +760,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="5" t="inlineStr"/>
-      <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="5" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="5" t="inlineStr"/>
-      <c r="K10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="n">
+        <v>-1.384754722939517</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>2.720555247624676</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.82253065776361</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>0.5519453909135635</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>-0.284467415633774</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>1.694112117619456</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
@@ -754,15 +786,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="5" t="inlineStr"/>
-      <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="5" t="inlineStr"/>
-      <c r="K11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="n">
+        <v>-4.702400446034093</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-1.135847984841499</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-2.889356158287031</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-2.982730967408772</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>-2.557434466311993</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>-0.972583218134767</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
@@ -771,15 +812,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="5" t="inlineStr"/>
-      <c r="G12" s="5" t="inlineStr"/>
-      <c r="H12" s="5" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr"/>
-      <c r="J12" s="5" t="inlineStr"/>
-      <c r="K12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="n">
+        <v>1.580562011359464</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>6.886427309067908</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>4.582706059436091</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>4.227535036599258</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>2.120845956709372</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>4.423648059763247</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
@@ -788,15 +838,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr"/>
-      <c r="D13" s="6" t="inlineStr"/>
-      <c r="E13" s="6" t="inlineStr"/>
-      <c r="F13" s="6" t="inlineStr"/>
-      <c r="G13" s="6" t="inlineStr"/>
-      <c r="H13" s="6" t="inlineStr"/>
-      <c r="I13" s="6" t="inlineStr"/>
-      <c r="J13" s="6" t="inlineStr"/>
-      <c r="K13" s="6" t="inlineStr"/>
+      <c r="C13" s="6" t="n">
+        <v>-0.2873382686161444</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>0.5645184822822839</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>0.1657407331379043</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>0.1112175368524585</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.05816121271892898</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.3463722374777395</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
@@ -805,15 +864,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr"/>
-      <c r="D14" s="6" t="inlineStr"/>
-      <c r="E14" s="6" t="inlineStr"/>
-      <c r="F14" s="6" t="inlineStr"/>
-      <c r="G14" s="6" t="inlineStr"/>
-      <c r="H14" s="6" t="inlineStr"/>
-      <c r="I14" s="6" t="inlineStr"/>
-      <c r="J14" s="6" t="inlineStr"/>
-      <c r="K14" s="6" t="inlineStr"/>
+      <c r="C14" s="6" t="n">
+        <v>-0.6974289132606886</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>-0.2148119002403212</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>-0.4173453861837841</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-0.4620741740307475</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.4384390492062922</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.1572110755774766</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
@@ -822,15 +890,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr"/>
-      <c r="D15" s="6" t="inlineStr"/>
-      <c r="E15" s="6" t="inlineStr"/>
-      <c r="F15" s="6" t="inlineStr"/>
-      <c r="G15" s="6" t="inlineStr"/>
-      <c r="H15" s="6" t="inlineStr"/>
-      <c r="I15" s="6" t="inlineStr"/>
-      <c r="J15" s="6" t="inlineStr"/>
-      <c r="K15" s="6" t="inlineStr"/>
+      <c r="C15" s="6" t="n">
+        <v>0.5255500767109695</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>2.317503920240525</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>1.567482901154114</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>1.333069411560499</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.5624379759638746</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>1.177742706637717</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -843,15 +920,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr"/>
-      <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="5" t="inlineStr"/>
-      <c r="F16" s="5" t="inlineStr"/>
-      <c r="G16" s="5" t="inlineStr"/>
-      <c r="H16" s="5" t="inlineStr"/>
-      <c r="I16" s="5" t="inlineStr"/>
-      <c r="J16" s="5" t="inlineStr"/>
-      <c r="K16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="n">
+        <v>-1.271021597484405</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-1.651492907823464</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-3.231609441748422</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-1.626042839059815</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>-2.269467977636673</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>-1.645602060077257</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
@@ -860,15 +946,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr"/>
-      <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="5" t="inlineStr"/>
-      <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr"/>
-      <c r="J17" s="5" t="inlineStr"/>
-      <c r="K17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="n">
+        <v>-5.201210993772257</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-6.011421362729958</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-7.528627642678531</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-5.890340543039718</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>-5.336313879935359</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>-4.725160814198837</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
@@ -877,15 +972,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr"/>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="inlineStr"/>
-      <c r="F18" s="5" t="inlineStr"/>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr"/>
-      <c r="J18" s="5" t="inlineStr"/>
-      <c r="K18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="n">
+        <v>3.10396733455716</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>2.086137993454449</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.3166395157667707</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>2.226805353900537</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>0.4691643022539975</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>0.9275824684754241</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
@@ -894,15 +998,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr"/>
-      <c r="D19" s="6" t="inlineStr"/>
-      <c r="E19" s="6" t="inlineStr"/>
-      <c r="F19" s="6" t="inlineStr"/>
-      <c r="G19" s="6" t="inlineStr"/>
-      <c r="H19" s="6" t="inlineStr"/>
-      <c r="I19" s="6" t="inlineStr"/>
-      <c r="J19" s="6" t="inlineStr"/>
-      <c r="K19" s="6" t="inlineStr"/>
+      <c r="C19" s="6" t="n">
+        <v>-0.2161571573876012</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>-0.280862271032561</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>-0.5372644620113349</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>-0.2703343479099988</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>-0.3816462111270831</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-0.2767334888353082</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n"/>
@@ -911,15 +1024,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr"/>
-      <c r="D20" s="6" t="inlineStr"/>
-      <c r="E20" s="6" t="inlineStr"/>
-      <c r="F20" s="6" t="inlineStr"/>
-      <c r="G20" s="6" t="inlineStr"/>
-      <c r="H20" s="6" t="inlineStr"/>
-      <c r="I20" s="6" t="inlineStr"/>
-      <c r="J20" s="6" t="inlineStr"/>
-      <c r="K20" s="6" t="inlineStr"/>
+      <c r="C20" s="6" t="n">
+        <v>-0.6583439650758184</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>-0.6932313480996398</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>-0.8403495498162558</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>-0.7115953981061054</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-0.6738098302095584</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>-0.6081222605161825</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
@@ -928,15 +1050,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr"/>
-      <c r="D21" s="6" t="inlineStr"/>
-      <c r="E21" s="6" t="inlineStr"/>
-      <c r="F21" s="6" t="inlineStr"/>
-      <c r="G21" s="6" t="inlineStr"/>
-      <c r="H21" s="6" t="inlineStr"/>
-      <c r="I21" s="6" t="inlineStr"/>
-      <c r="J21" s="6" t="inlineStr"/>
-      <c r="K21" s="6" t="inlineStr"/>
+      <c r="C21" s="6" t="n">
+        <v>0.9463161117853474</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>0.6974983354899142</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>0.1637159035247033</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>0.799923502925707</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>0.1210480326733341</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>0.2209713958148682</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -949,15 +1080,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr"/>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="5" t="inlineStr"/>
-      <c r="G22" s="5" t="inlineStr"/>
-      <c r="H22" s="5" t="inlineStr"/>
-      <c r="I22" s="5" t="inlineStr"/>
-      <c r="J22" s="5" t="inlineStr"/>
-      <c r="K22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="n">
+        <v>0.4213974660380877</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>4.063105519067207</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>3.342391120931365</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>5.287769084236877</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>1.730900770180926</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>4.586419865701006</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n"/>
@@ -966,15 +1106,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr"/>
-      <c r="D23" s="5" t="inlineStr"/>
-      <c r="E23" s="5" t="inlineStr"/>
-      <c r="F23" s="5" t="inlineStr"/>
-      <c r="G23" s="5" t="inlineStr"/>
-      <c r="H23" s="5" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="5" t="inlineStr"/>
-      <c r="K23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="n">
+        <v>-4.459063309452793</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-0.6964430279751158</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-0.8355666095340084</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>1.39100377815334</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>-1.623905104214933</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>1.447320295704852</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n"/>
@@ -983,15 +1132,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr"/>
-      <c r="D24" s="5" t="inlineStr"/>
-      <c r="E24" s="5" t="inlineStr"/>
-      <c r="F24" s="5" t="inlineStr"/>
-      <c r="G24" s="5" t="inlineStr"/>
-      <c r="H24" s="5" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr"/>
-      <c r="J24" s="5" t="inlineStr"/>
-      <c r="K24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="n">
+        <v>4.97934296259448</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>9.573495554332695</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>8.675159096993166</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>9.405525801245822</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>5.048567181149289</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>7.834454680193589</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n"/>
@@ -1000,15 +1158,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr"/>
-      <c r="D25" s="6" t="inlineStr"/>
-      <c r="E25" s="6" t="inlineStr"/>
-      <c r="F25" s="6" t="inlineStr"/>
-      <c r="G25" s="6" t="inlineStr"/>
-      <c r="H25" s="6" t="inlineStr"/>
-      <c r="I25" s="6" t="inlineStr"/>
-      <c r="J25" s="6" t="inlineStr"/>
-      <c r="K25" s="6" t="inlineStr"/>
+      <c r="C25" s="6" t="n">
+        <v>0.1144402880448873</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>1.103430854320314</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>2.000766203210563</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>3.165275783515959</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>0.6244769744127217</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>1.654695433996478</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n"/>
@@ -1017,15 +1184,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr"/>
-      <c r="D26" s="6" t="inlineStr"/>
-      <c r="E26" s="6" t="inlineStr"/>
-      <c r="F26" s="6" t="inlineStr"/>
-      <c r="G26" s="6" t="inlineStr"/>
-      <c r="H26" s="6" t="inlineStr"/>
-      <c r="I26" s="6" t="inlineStr"/>
-      <c r="J26" s="6" t="inlineStr"/>
-      <c r="K26" s="6" t="inlineStr"/>
+      <c r="C26" s="6" t="n">
+        <v>-0.79361840024811</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>-0.3246632791114792</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>-0.778287321532665</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>-0.1478715682687215</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>-0.4355820324417135</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>0.2439360345364866</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n"/>
@@ -1034,15 +1210,20 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr"/>
-      <c r="D27" s="6" t="inlineStr"/>
+      <c r="C27" s="6" t="n">
+        <v>3.425802023094787</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>6.596313179208785</v>
+      </c>
       <c r="E27" s="6" t="inlineStr"/>
       <c r="F27" s="6" t="inlineStr"/>
-      <c r="G27" s="6" t="inlineStr"/>
-      <c r="H27" s="6" t="inlineStr"/>
-      <c r="I27" s="6" t="inlineStr"/>
-      <c r="J27" s="6" t="inlineStr"/>
-      <c r="K27" s="6" t="inlineStr"/>
+      <c r="G27" s="6" t="n">
+        <v>3.637358846970638</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>6.389155946790423</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -1055,15 +1236,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr"/>
-      <c r="D28" s="5" t="inlineStr"/>
-      <c r="E28" s="5" t="inlineStr"/>
-      <c r="F28" s="5" t="inlineStr"/>
-      <c r="G28" s="5" t="inlineStr"/>
-      <c r="H28" s="5" t="inlineStr"/>
-      <c r="I28" s="5" t="inlineStr"/>
-      <c r="J28" s="5" t="inlineStr"/>
-      <c r="K28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="n">
+        <v>-1.812761025758515</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>0.2502970435946314</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>-0.2456641584589185</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>-0.03907753938857811</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>-1.050601845084293</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>0.1280448238634734</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n"/>
@@ -1072,15 +1262,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr"/>
-      <c r="D29" s="5" t="inlineStr"/>
-      <c r="E29" s="5" t="inlineStr"/>
-      <c r="F29" s="5" t="inlineStr"/>
-      <c r="G29" s="5" t="inlineStr"/>
-      <c r="H29" s="5" t="inlineStr"/>
-      <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr"/>
-      <c r="K29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="n">
+        <v>-3.787040700977091</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>-2.162047958004878</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>-2.256589831113493</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>-1.995892255837424</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>-2.355960782260821</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>-1.472376734987093</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n"/>
@@ -1089,15 +1288,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr"/>
-      <c r="D30" s="5" t="inlineStr"/>
-      <c r="E30" s="5" t="inlineStr"/>
-      <c r="F30" s="5" t="inlineStr"/>
-      <c r="G30" s="5" t="inlineStr"/>
-      <c r="H30" s="5" t="inlineStr"/>
-      <c r="I30" s="5" t="inlineStr"/>
-      <c r="J30" s="5" t="inlineStr"/>
-      <c r="K30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="n">
+        <v>-0.07005313059223119</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>2.38927843796134</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>1.74237154932115</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>2.391735551034833</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>0.4157085320582562</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>1.720436174459462</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n"/>
@@ -1106,15 +1314,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr"/>
-      <c r="D31" s="6" t="inlineStr"/>
-      <c r="E31" s="6" t="inlineStr"/>
-      <c r="F31" s="6" t="inlineStr"/>
-      <c r="G31" s="6" t="inlineStr"/>
-      <c r="H31" s="6" t="inlineStr"/>
-      <c r="I31" s="6" t="inlineStr"/>
-      <c r="J31" s="6" t="inlineStr"/>
-      <c r="K31" s="6" t="inlineStr"/>
+      <c r="C31" s="6" t="n">
+        <v>-0.2893340511308369</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>0.03994980947861226</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>-0.04403673850658209</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>-0.007004877692906297</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>-0.1771683625773282</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>0.02159285355012282</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n"/>
@@ -1123,15 +1340,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr"/>
-      <c r="D32" s="6" t="inlineStr"/>
-      <c r="E32" s="6" t="inlineStr"/>
-      <c r="F32" s="6" t="inlineStr"/>
-      <c r="G32" s="6" t="inlineStr"/>
-      <c r="H32" s="6" t="inlineStr"/>
-      <c r="I32" s="6" t="inlineStr"/>
-      <c r="J32" s="6" t="inlineStr"/>
-      <c r="K32" s="6" t="inlineStr"/>
+      <c r="C32" s="6" t="n">
+        <v>-0.5187116693577744</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>-0.3026633697059845</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>-0.3415514451614078</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>-0.3032662606551955</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>-0.3493577879069318</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>-0.2218353720167917</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n"/>
@@ -1140,15 +1366,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr"/>
-      <c r="D33" s="6" t="inlineStr"/>
-      <c r="E33" s="6" t="inlineStr"/>
-      <c r="F33" s="6" t="inlineStr"/>
-      <c r="G33" s="6" t="inlineStr"/>
-      <c r="H33" s="6" t="inlineStr"/>
-      <c r="I33" s="6" t="inlineStr"/>
-      <c r="J33" s="6" t="inlineStr"/>
-      <c r="K33" s="6" t="inlineStr"/>
+      <c r="C33" s="6" t="n">
+        <v>-0.001660426927646046</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>0.4568341041934728</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>0.3710438209569048</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>0.5559549968233254</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>0.08972345025135635</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>0.3378893321893473</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1159,11 +1394,11 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A22:A27"/>
     <mergeCell ref="A4:A9"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A10:A15"/>
     <mergeCell ref="A28:A33"/>
